--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128150350</v>
       </c>
       <c r="B2" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128150348</v>
       </c>
       <c r="B4" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128150346</v>
       </c>
       <c r="B6" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128150342</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128150357</v>
       </c>
       <c r="B11" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128150333</v>
+        <v>128150355</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552123</v>
+        <v>552191</v>
       </c>
       <c r="R14" t="n">
-        <v>7193272</v>
+        <v>7193440</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128150355</v>
+        <v>128150333</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552191</v>
+        <v>552123</v>
       </c>
       <c r="R15" t="n">
-        <v>7193440</v>
+        <v>7193272</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128150350</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128150348</v>
       </c>
       <c r="B4" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128150346</v>
       </c>
       <c r="B6" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128150342</v>
       </c>
       <c r="B7" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128150357</v>
       </c>
       <c r="B11" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128150355</v>
+        <v>128150333</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552191</v>
+        <v>552123</v>
       </c>
       <c r="R14" t="n">
-        <v>7193440</v>
+        <v>7193272</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128150333</v>
+        <v>128150355</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552123</v>
+        <v>552191</v>
       </c>
       <c r="R15" t="n">
-        <v>7193272</v>
+        <v>7193440</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128150350</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128150335</v>
       </c>
       <c r="B3" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128150348</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128150331</v>
       </c>
       <c r="B5" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128150346</v>
       </c>
       <c r="B6" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128150342</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128150353</v>
       </c>
       <c r="B8" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128150322</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128150357</v>
       </c>
       <c r="B11" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128150344</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128150333</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128150355</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128150350</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128150335</v>
       </c>
       <c r="B3" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128150348</v>
       </c>
       <c r="B4" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128150331</v>
       </c>
       <c r="B5" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128150346</v>
       </c>
       <c r="B6" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128150342</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128150353</v>
       </c>
       <c r="B8" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128150322</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128150357</v>
       </c>
       <c r="B11" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128150344</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128150333</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128150355</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128150350</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128150335</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128150348</v>
       </c>
       <c r="B4" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128150331</v>
       </c>
       <c r="B5" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128150346</v>
       </c>
       <c r="B6" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128150342</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128150353</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128150322</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128150357</v>
       </c>
       <c r="B11" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128150344</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128150333</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128150355</v>
       </c>
       <c r="B15" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128150350</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128150335</v>
       </c>
       <c r="B3" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128150348</v>
       </c>
       <c r="B4" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128150331</v>
       </c>
       <c r="B5" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128150346</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128150342</v>
       </c>
       <c r="B7" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128150353</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128150322</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128150357</v>
       </c>
       <c r="B11" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128150344</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128150333</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128150355</v>
       </c>
       <c r="B15" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128150333</v>
+        <v>128150355</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552123</v>
+        <v>552191</v>
       </c>
       <c r="R14" t="n">
-        <v>7193272</v>
+        <v>7193440</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128150355</v>
+        <v>128150333</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552191</v>
+        <v>552123</v>
       </c>
       <c r="R15" t="n">
-        <v>7193440</v>
+        <v>7193272</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 33322-2025 artfynd.xlsx
+++ b/artfynd/A 33322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128150350</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128150348</v>
       </c>
       <c r="B4" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128150346</v>
       </c>
       <c r="B6" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128150342</v>
       </c>
       <c r="B7" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128150329</v>
       </c>
       <c r="B9" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128150357</v>
       </c>
       <c r="B11" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128150355</v>
+        <v>128150333</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552191</v>
+        <v>552123</v>
       </c>
       <c r="R14" t="n">
-        <v>7193440</v>
+        <v>7193272</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128150333</v>
+        <v>128150355</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552123</v>
+        <v>552191</v>
       </c>
       <c r="R15" t="n">
-        <v>7193272</v>
+        <v>7193440</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
